--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>72.14562346583291</v>
+        <v>11.72366381319785</v>
       </c>
       <c r="D2" t="n">
-        <v>68.9531149847039</v>
+        <v>11.20488118501438</v>
       </c>
       <c r="E2" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F2" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.50392072063177</v>
+        <v>11.45688711710266</v>
       </c>
       <c r="D3" t="n">
-        <v>57.92985839055813</v>
+        <v>9.413601988465697</v>
       </c>
       <c r="E3" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F3" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.84326231097667</v>
+        <v>9.399530125533708</v>
       </c>
       <c r="D4" t="n">
-        <v>58.23367113528611</v>
+        <v>9.462971559483993</v>
       </c>
       <c r="E4" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F4" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.25225756091407</v>
+        <v>5.890991853648536</v>
       </c>
       <c r="D5" t="n">
-        <v>35.54087066698052</v>
+        <v>5.775391483384335</v>
       </c>
       <c r="E5" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F5" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>58.26817365514083</v>
+        <v>9.468578218960385</v>
       </c>
       <c r="D6" t="n">
-        <v>45.72049729351686</v>
+        <v>7.429580810196489</v>
       </c>
       <c r="E6" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F6" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.54424514107449</v>
+        <v>3.663439835424605</v>
       </c>
       <c r="D7" t="n">
-        <v>22.11780264465078</v>
+        <v>3.594142929755751</v>
       </c>
       <c r="E7" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F7" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.29343010039122</v>
+        <v>4.922682391313574</v>
       </c>
       <c r="D8" t="n">
-        <v>28.85358397202714</v>
+        <v>4.688707395454411</v>
       </c>
       <c r="E8" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F8" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>46.50996267397473</v>
+        <v>7.557868934520894</v>
       </c>
       <c r="D9" t="n">
-        <v>41.56180496186338</v>
+        <v>6.7537933063028</v>
       </c>
       <c r="E9" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F9" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.47561720391341</v>
+        <v>3.16478779563593</v>
       </c>
       <c r="D10" t="n">
-        <v>18.31968064687859</v>
+        <v>2.976948105117771</v>
       </c>
       <c r="E10" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F10" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>14.44588059738753</v>
+        <v>2.347455597075473</v>
       </c>
       <c r="D11" t="n">
-        <v>12.97514903888207</v>
+        <v>2.108461718818337</v>
       </c>
       <c r="E11" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F11" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>51.58791037861479</v>
+        <v>8.383035436524905</v>
       </c>
       <c r="D12" t="n">
-        <v>50.22150653566171</v>
+        <v>8.160994812045029</v>
       </c>
       <c r="E12" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F12" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.68297289119908</v>
+        <v>6.285983094819851</v>
       </c>
       <c r="D13" t="n">
-        <v>29.99587959760947</v>
+        <v>4.874330434611539</v>
       </c>
       <c r="E13" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F13" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82593812130719</v>
+        <v>2.246714944712418</v>
       </c>
       <c r="D14" t="n">
-        <v>13.95997001702097</v>
+        <v>2.268495127765908</v>
       </c>
       <c r="E14" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F14" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>57.62813191429483</v>
+        <v>9.364571436072911</v>
       </c>
       <c r="D15" t="n">
-        <v>56.3436364833429</v>
+        <v>9.155840928543221</v>
       </c>
       <c r="E15" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F15" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>16.55057969228648</v>
+        <v>2.689469199996553</v>
       </c>
       <c r="D16" t="n">
-        <v>15.32864629774003</v>
+        <v>2.490905023382755</v>
       </c>
       <c r="E16" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F16" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>34.3084776440358</v>
+        <v>5.575127617155818</v>
       </c>
       <c r="D17" t="n">
-        <v>22.48926234877984</v>
+        <v>3.654505131676725</v>
       </c>
       <c r="E17" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F17" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>30.61559757672303</v>
+        <v>4.975034606217492</v>
       </c>
       <c r="D18" t="n">
-        <v>31.96518937693953</v>
+        <v>5.194343273752674</v>
       </c>
       <c r="E18" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F18" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>9.675046385324256</v>
+        <v>1.572195037615192</v>
       </c>
       <c r="D19" t="n">
-        <v>9.52430208061814</v>
+        <v>1.547699088100448</v>
       </c>
       <c r="E19" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F19" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>68.4865499262643</v>
+        <v>11.12906436301795</v>
       </c>
       <c r="D20" t="n">
-        <v>67.48610870663036</v>
+        <v>10.96649266482743</v>
       </c>
       <c r="E20" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F20" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>6.581591435943388</v>
+        <v>1.069508608340801</v>
       </c>
       <c r="D21" t="n">
-        <v>8.760867127989329</v>
+        <v>1.423640908298266</v>
       </c>
       <c r="E21" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F21" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>29.03581510613389</v>
+        <v>4.718319954746756</v>
       </c>
       <c r="D22" t="n">
-        <v>11.26066477461288</v>
+        <v>1.829858025874593</v>
       </c>
       <c r="E22" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F22" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>33.42547770236917</v>
+        <v>5.43164012663499</v>
       </c>
       <c r="D23" t="n">
-        <v>33.2262941245503</v>
+        <v>5.399272795239424</v>
       </c>
       <c r="E23" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F23" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>46.22496040551084</v>
+        <v>7.511556065895512</v>
       </c>
       <c r="D24" t="n">
-        <v>46.47848407304541</v>
+        <v>7.55275366186988</v>
       </c>
       <c r="E24" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F24" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>28.89933800272316</v>
+        <v>4.696142425442514</v>
       </c>
       <c r="D25" t="n">
-        <v>9.498750042020761</v>
+        <v>1.543546881828374</v>
       </c>
       <c r="E25" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F25" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>28.04207580801414</v>
+        <v>4.556837318802298</v>
       </c>
       <c r="D26" t="n">
-        <v>5.310845886276294</v>
+        <v>0.8630124565198978</v>
       </c>
       <c r="E26" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F26" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>78.18205119288987</v>
+        <v>12.70458331884461</v>
       </c>
       <c r="D27" t="n">
-        <v>77.84283175562081</v>
+        <v>12.64946016028838</v>
       </c>
       <c r="E27" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F27" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>61.37408976548549</v>
+        <v>9.973289586891392</v>
       </c>
       <c r="D28" t="n">
-        <v>56.01969918563314</v>
+        <v>9.103201117665385</v>
       </c>
       <c r="E28" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F28" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>82.79090259821193</v>
+        <v>13.45352167220944</v>
       </c>
       <c r="D29" t="n">
-        <v>82.69959679263604</v>
+        <v>13.43868447880336</v>
       </c>
       <c r="E29" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F29" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>76.22507978079197</v>
+        <v>12.3865754643787</v>
       </c>
       <c r="D30" t="n">
-        <v>72.63348420872103</v>
+        <v>11.80294118391717</v>
       </c>
       <c r="E30" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F30" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>52.15773299771401</v>
+        <v>8.475631612128527</v>
       </c>
       <c r="D31" t="n">
-        <v>45.22980587909407</v>
+        <v>7.349843455352787</v>
       </c>
       <c r="E31" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F31" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>78.78552759948079</v>
+        <v>12.80264823491563</v>
       </c>
       <c r="D32" t="n">
-        <v>78.9094464463459</v>
+        <v>12.82278504753121</v>
       </c>
       <c r="E32" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F32" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>66.72123528524945</v>
+        <v>10.84220073385304</v>
       </c>
       <c r="D33" t="n">
-        <v>66.82861994068185</v>
+        <v>10.8596507403608</v>
       </c>
       <c r="E33" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F33" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>30.24797275557614</v>
+        <v>4.915295572781123</v>
       </c>
       <c r="D34" t="n">
-        <v>30.2915356560864</v>
+        <v>4.92237454411404</v>
       </c>
       <c r="E34" t="n">
-        <v>22.21397175118556</v>
+        <v>3.609770409567654</v>
       </c>
       <c r="F34" t="n">
-        <v>23.32863432092427</v>
+        <v>3.790903077150194</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
